--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488261_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488261_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.6386</v>
+        <v>8.6812</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0554</v>
+        <v>6.295</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5832</v>
+        <v>2.3862</v>
       </c>
       <c r="G2" t="n">
         <v>5.6136</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7661</v>
+        <v>1.8087</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0519</v>
+        <v>1.2914</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7143</v>
+        <v>0.5173</v>
       </c>
       <c r="V2" t="n">
         <v>1.2589</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7183</v>
+        <v>8.1593</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2473</v>
+        <v>6.639</v>
       </c>
       <c r="F3" t="n">
-        <v>1.471</v>
+        <v>1.5203</v>
       </c>
       <c r="G3" t="n">
         <v>4.0924</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0977</v>
+        <v>0.3432</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5596</v>
+        <v>-0.1679</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4618</v>
+        <v>0.5111</v>
       </c>
       <c r="V3" t="n">
         <v>0.9444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5345</v>
+        <v>6.5515</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2253</v>
+        <v>3.2915</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3092</v>
+        <v>3.26</v>
       </c>
       <c r="G4" t="n">
         <v>2.8066</v>
@@ -766,13 +766,13 @@
         <v>3.1499</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8935999999999999</v>
+        <v>0.9106</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6914</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2022</v>
+        <v>0.1529</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3155</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2116</v>
+        <v>4.658</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9789</v>
+        <v>3.4254</v>
       </c>
       <c r="F5" t="n">
         <v>1.2326</v>
@@ -844,10 +844,10 @@
         <v>2.9646</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4129</v>
+        <v>0.0336</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6354</v>
+        <v>-0.189</v>
       </c>
       <c r="U5" t="n">
         <v>0.2226</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5678</v>
+        <v>3.4912</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3726</v>
+        <v>3.5914</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1952</v>
+        <v>-0.1002</v>
       </c>
       <c r="G6" t="n">
         <v>2.894</v>
@@ -922,13 +922,13 @@
         <v>2.9646</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8389</v>
+        <v>0.7623</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8556</v>
+        <v>1.0744</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0167</v>
+        <v>-0.3121</v>
       </c>
       <c r="V6" t="n">
         <v>-2.2033</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7255</v>
+        <v>1.6517</v>
       </c>
       <c r="E7" t="n">
         <v>0.0939</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6317</v>
+        <v>1.5578</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0541</v>
@@ -1000,13 +1000,13 @@
         <v>2.594</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4096</v>
+        <v>0.3358</v>
       </c>
       <c r="T7" t="n">
         <v>0.09329999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3163</v>
+        <v>0.2425</v>
       </c>
       <c r="V7" t="n">
         <v>0.6289</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4266</v>
+        <v>1.39</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7267</v>
+        <v>0.5423</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6999</v>
+        <v>0.8477</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0024</v>
@@ -1156,13 +1156,13 @@
         <v>2.594</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1495</v>
+        <v>0.1129</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.5954</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6302</v>
+        <v>-0.4825</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>J. CACHO REGUERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.241</v>
+        <v>0.5617</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2305</v>
+        <v>0.2361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4715</v>
+        <v>0.3256</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9739</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6836</v>
+        <v>-0.1236</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2903</v>
+        <v>-0.8265</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2445</v>
+        <v>-0.3294</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1201</v>
+        <v>0.3435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1244</v>
+        <v>-0.673</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2184</v>
+        <v>-0.6207</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8037</v>
+        <v>-0.4671</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4147</v>
+        <v>-0.1536</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6676</v>
+        <v>0.7411</v>
       </c>
       <c r="S10" t="n">
-        <v>2.0111</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3043</v>
+        <v>0.5655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2932</v>
+        <v>0.2052</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CACHO REGUERO</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2152</v>
+        <v>-0.8181</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4177</v>
+        <v>-1.4374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2025</v>
+        <v>0.6192</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.9739</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1236</v>
+        <v>-0.6836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8265</v>
+        <v>-0.2903</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3294</v>
+        <v>0.2445</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3435</v>
+        <v>0.1201</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.673</v>
+        <v>0.1244</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6207</v>
+        <v>-1.2184</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4671</v>
+        <v>-0.8037</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1536</v>
+        <v>-0.4147</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7411</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0062</v>
+        <v>0.9519</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0883</v>
+        <v>1.0974</v>
       </c>
       <c r="U11" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.1455</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8408</v>
+        <v>-0.9993</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1311</v>
+        <v>-2.898</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2903</v>
+        <v>1.8987</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4153</v>
+        <v>-2.6681</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5489</v>
+        <v>-1.0306</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-1.6375</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.3886</v>
+        <v>-2.0649</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8293</v>
+        <v>-0.1892</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5592</v>
+        <v>-1.8756</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0267</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7196</v>
+        <v>-0.8414</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3071</v>
+        <v>0.2381</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2234</v>
+        <v>2.594</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6098</v>
+        <v>0.9277</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2574</v>
+        <v>1.0197</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3524</v>
+        <v>-0.092</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>H. SANTOS PARRA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9515</v>
+        <v>-1.0263</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0724</v>
+        <v>-1.1196</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1209</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.1643</v>
+        <v>-2.4153</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.0306</v>
+        <v>-1.5489</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1337</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.8742</v>
+        <v>-1.3886</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6099</v>
+        <v>-0.8293</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2643</v>
+        <v>-0.5592</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2901</v>
+        <v>-1.0267</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4207</v>
+        <v>-0.7196</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1306</v>
+        <v>-0.3071</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7411</v>
+        <v>2.2234</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7411</v>
+        <v>2.2234</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2134</v>
+        <v>0.4244</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1977</v>
+        <v>0.2689</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0157</v>
+        <v>0.1554</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.315</v>
+        <v>-1.2589</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>H. SANTOS PARRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6204</v>
+        <v>-1.2233</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.3467</v>
+        <v>-1.5166</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7264</v>
+        <v>0.2933</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6681</v>
+        <v>-2.1643</v>
       </c>
       <c r="H14" t="n">
         <v>-1.0306</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6375</v>
+        <v>-1.1337</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0649</v>
+        <v>-1.8742</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1892</v>
+        <v>-0.6099</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8756</v>
+        <v>-1.2643</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.2901</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8414</v>
+        <v>-0.4207</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2381</v>
+        <v>0.1306</v>
       </c>
       <c r="P14" t="n">
         <v>0.7411</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6934</v>
+        <v>0.5148</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.429</v>
+        <v>0.3581</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2644</v>
+        <v>0.1567</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>31.00219999999999</v>
+        <v>32.6438</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0679</v>
+        <v>18.7092</v>
       </c>
       <c r="F15" t="n">
-        <v>13.9344</v>
+        <v>13.9345</v>
       </c>
       <c r="G15" t="n">
         <v>10.5543</v>
@@ -1624,13 +1624,13 @@
         <v>27.7929</v>
       </c>
       <c r="S15" t="n">
-        <v>6.254999999999999</v>
+        <v>7.8966</v>
       </c>
       <c r="T15" t="n">
-        <v>5.123599999999999</v>
+        <v>6.764800000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1315</v>
+        <v>1.1316</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6300000000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4274</v>
+        <v>2.7413</v>
       </c>
       <c r="E16" t="n">
-        <v>4.093</v>
+        <v>3.1137</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6656</v>
+        <v>-0.3724</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7304</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0461</v>
+        <v>0.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.302</v>
+        <v>0.3227</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2559</v>
+        <v>0.0373</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2547</v>
+        <v>0.4591</v>
       </c>
       <c r="E18" t="n">
         <v>0.5797</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.325</v>
+        <v>-0.1206</v>
       </c>
       <c r="G18" t="n">
         <v>2.1507</v>
@@ -1858,13 +1858,13 @@
         <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8225</v>
+        <v>-0.618</v>
       </c>
       <c r="T18" t="n">
         <v>-0.2524</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.57</v>
+        <v>-0.3656</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>E. COELHO PAULINO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4724</v>
+        <v>-0.3673</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-0.9597</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2579</v>
+        <v>0.5924</v>
       </c>
       <c r="G19" t="n">
-        <v>0.677</v>
+        <v>1.7663</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4097</v>
+        <v>2.1239</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2673</v>
+        <v>-0.3577</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1285</v>
+        <v>2.4932</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4851</v>
+        <v>2.4518</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6434</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4515</v>
+        <v>-0.727</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.3278</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3761</v>
+        <v>-0.3991</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4823</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0179</v>
+        <v>-0.6131</v>
       </c>
       <c r="T19" t="n">
-        <v>0.291</v>
+        <v>-0.0796</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2731</v>
+        <v>-0.5335</v>
       </c>
       <c r="V19" t="n">
-        <v>0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. COELHO PAULINO</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8724</v>
+        <v>-0.5463</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3514</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.479</v>
+        <v>0.1841</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7663</v>
+        <v>0.677</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1239</v>
+        <v>0.4097</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3577</v>
+        <v>0.2673</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4932</v>
+        <v>1.1285</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4518</v>
+        <v>0.4851</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0415</v>
+        <v>0.6434</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.727</v>
+        <v>-0.4515</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3278</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3991</v>
+        <v>-0.3761</v>
       </c>
       <c r="P20" t="n">
+        <v>-1.4823</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-2.7793</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-4.6322</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1182</v>
+        <v>-0.056</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4713</v>
+        <v>0.291</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6469</v>
+        <v>-0.347</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2589</v>
+        <v>0.315</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2589</v>
+        <v>0.6294</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5971</v>
+        <v>-2.6853</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4453</v>
+        <v>0.9557</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.0424</v>
+        <v>-3.641</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2508</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2907</v>
+        <v>-0.379</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6491</v>
+        <v>0.1595</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9399</v>
+        <v>-0.5385</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.314</v>
+        <v>-2.774</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4942</v>
+        <v>-0.5921</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8198</v>
+        <v>-2.1819</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5705</v>
@@ -2170,13 +2170,13 @@
         <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1876</v>
+        <v>-0.6476</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2226</v>
+        <v>-0.3205</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.965</v>
+        <v>-0.3271</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>I. FERNANDEZ MEGIAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8013</v>
+        <v>-3.3953</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4624</v>
+        <v>-2.7489</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.339</v>
+        <v>-0.6463</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6793</v>
+        <v>-1.04</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8053</v>
+        <v>-0.011</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.874</v>
+        <v>-1.029</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7919</v>
+        <v>-0.1677</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8334</v>
+        <v>0.4851</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9586</v>
+        <v>-0.6529</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8874</v>
+        <v>-0.8723</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.972</v>
+        <v>-0.4961</v>
       </c>
       <c r="O23" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.3761</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1853</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1117</v>
+        <v>-3.7057</v>
       </c>
       <c r="R23" t="n">
-        <v>1.297</v>
+        <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6223</v>
+        <v>-0.3171</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1269</v>
+        <v>-0.1343</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7491</v>
+        <v>-0.1828</v>
       </c>
       <c r="V23" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
-        <v>0.0005</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MEGIAS</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0727</v>
+        <v>-3.4738</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1406</v>
+        <v>-3.4624</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9321</v>
+        <v>-0.0114</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.04</v>
+        <v>-3.6793</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.011</v>
+        <v>-1.8053</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.029</v>
+        <v>-1.874</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1677</v>
+        <v>-2.7919</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4851</v>
+        <v>-0.8334</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6529</v>
+        <v>-1.9586</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8723</v>
+        <v>-0.8874</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4961</v>
+        <v>-0.972</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3761</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0382</v>
+        <v>0.1853</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.7057</v>
+        <v>-1.1117</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9946</v>
+        <v>-0.2947</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.526</v>
+        <v>0.1269</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4686</v>
+        <v>-0.4216</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2589</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.0247</v>
+        <v>-5.0109</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7524</v>
+        <v>-3.5565</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2723</v>
+        <v>-1.4543</v>
       </c>
       <c r="G25" t="n">
         <v>-2.4623</v>
@@ -2404,13 +2404,13 @@
         <v>0.3706</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6163</v>
+        <v>-0.6025</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7113</v>
+        <v>-0.5154</v>
       </c>
       <c r="U25" t="n">
-        <v>0.095</v>
+        <v>-0.0871</v>
       </c>
       <c r="V25" t="n">
         <v>1.5744</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.2643</v>
+        <v>-7.5628</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.7777</v>
+        <v>-3.2881</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.4866</v>
+        <v>-4.2747</v>
       </c>
       <c r="G26" t="n">
         <v>-2.0021</v>
@@ -2482,13 +2482,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0563</v>
+        <v>-0.3547</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9302</v>
+        <v>-0.4405</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1261</v>
+        <v>0.0858</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9444</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.4756</v>
+        <v>-7.986</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.5538</v>
+        <v>-5.4559</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.9218</v>
+        <v>-2.5301</v>
       </c>
       <c r="G27" t="n">
         <v>-4.6231</v>
@@ -2560,13 +2560,13 @@
         <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6106</v>
+        <v>-0.1209</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3867</v>
+        <v>-0.2888</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.2239</v>
+        <v>0.1679</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5744</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-31.0021</v>
+        <v>-28.391</v>
       </c>
       <c r="E28" t="n">
         <v>-13.9345</v>
       </c>
       <c r="F28" t="n">
-        <v>-17.0677</v>
+        <v>-14.4562</v>
       </c>
       <c r="G28" t="n">
         <v>-10.5542</v>
       </c>
       <c r="H28" t="n">
-        <v>-5.8322</v>
+        <v>-5.832199999999999</v>
       </c>
       <c r="I28" t="n">
         <v>-4.722</v>
@@ -2638,13 +2638,13 @@
         <v>12.9702</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.2551</v>
+        <v>-3.6436</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.1315</v>
+        <v>-1.1314</v>
       </c>
       <c r="U28" t="n">
-        <v>-5.1235</v>
+        <v>-2.5122</v>
       </c>
       <c r="V28" t="n">
         <v>0.6300999999999999</v>
